--- a/0_Admin/Checklist_Marks_FS2026.xlsx
+++ b/0_Admin/Checklist_Marks_FS2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr backupFile="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/shared.zhaw.ch/T-ISC-ET-PM4/0_Admin/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\ETPM4\Eval\PM4-003-Thursday\Grebnevs-Perri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2E13C7-EAEE-4E4F-9D7E-6425BBF9B751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1519FC-D7AC-401C-8F3B-AB7AB04AF501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-10200" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>Students</t>
   </si>
@@ -141,14 +141,24 @@
   </si>
   <si>
     <t xml:space="preserve">Clarity &amp; Readability, Correctness, Completeness ... </t>
+  </si>
+  <si>
+    <t>Thomas Perri</t>
+  </si>
+  <si>
+    <t>Bogdans Grebnevs</t>
+  </si>
+  <si>
+    <t>no complex signal demonstrated</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -199,7 +209,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -208,6 +218,8 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
@@ -517,17 +529,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" style="5"/>
-    <col min="5" max="5" width="8.83203125" style="2"/>
+    <col min="2" max="2" width="45.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.796875" style="5"/>
+    <col min="5" max="5" width="8.796875" style="2"/>
     <col min="6" max="6" width="80.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -547,20 +559,28 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -570,56 +590,56 @@
       <c r="D11" s="5">
         <v>0.05</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="9">
         <f>AVERAGE(C12:C15)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>5.875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C13" s="8">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="2">
-        <v>4</v>
+      <c r="C17" s="9">
+        <v>5.875</v>
       </c>
       <c r="D17" s="5">
         <v>0.05</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="9">
         <f>C17</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5.875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -627,39 +647,39 @@
       <c r="D21" s="5">
         <v>0.15</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="9">
         <f>AVERAGE(C22:C25)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5.583333333333333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>33</v>
       </c>
       <c r="C24" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -667,42 +687,45 @@
       <c r="D27" s="5">
         <v>0.15</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="9">
         <f>AVERAGE(C28:C31)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C28" s="8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B29" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C29" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5.5</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>33</v>
       </c>
       <c r="C30" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -717,7 +740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>19</v>
       </c>
@@ -725,7 +748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>28</v>
       </c>
@@ -733,7 +756,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>20</v>
       </c>
@@ -741,7 +764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>29</v>
       </c>
@@ -749,7 +772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>21</v>
       </c>
@@ -757,7 +780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>22</v>
       </c>
@@ -765,7 +788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>12</v>
       </c>
@@ -773,7 +796,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>32</v>
       </c>
@@ -781,7 +804,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -799,7 +822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -811,7 +834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
         <v>7</v>
       </c>
@@ -819,7 +842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>8</v>
       </c>
@@ -827,7 +850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>27</v>
       </c>
@@ -835,7 +858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
         <v>25</v>
       </c>
@@ -843,7 +866,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
         <v>26</v>
       </c>
@@ -851,7 +874,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
         <v>11</v>
       </c>
@@ -859,7 +882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>24</v>
       </c>
@@ -877,7 +900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A58" s="3" t="s">
         <v>3</v>
       </c>
@@ -888,7 +911,7 @@
       </c>
       <c r="E58" s="4">
         <f>D11*E11+D17*E17+D21*E21+D27*E27+D33*E33+D44*E44+D46*E46+D55*E55</f>
-        <v>3.9999999999999996</v>
+        <v>4.6500000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/0_Admin/Checklist_Marks_FS2026.xlsx
+++ b/0_Admin/Checklist_Marks_FS2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\ETPM4\Eval\PM4-003-Thursday\Grebnevs-Perri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1519FC-D7AC-401C-8F3B-AB7AB04AF501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CA5375-63EC-417C-B53C-C071BB6D6C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4650" yWindow="3263" windowWidth="16875" windowHeight="10432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>Students</t>
   </si>
@@ -150,6 +150,22 @@
   </si>
   <si>
     <t>no complex signal demonstrated</t>
+  </si>
+  <si>
+    <t>Interim Grading</t>
+  </si>
+  <si>
+    <t>SD card logging, ECG measurement for comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good use case idea, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No live demonstration </t>
+  </si>
+  <si>
+    <t>Minor pronunciation inconsistencies, overall good. 
+One voice over two would be more ideal (loudness varies). Very data/tech-detail-heavy.</t>
   </si>
 </sst>
 </file>
@@ -209,7 +225,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -220,6 +236,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
@@ -528,7 +548,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -539,7 +559,7 @@
     <col min="6" max="6" width="80.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -558,8 +578,11 @@
       <c r="F1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -567,20 +590,20 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -594,8 +617,16 @@
         <f>AVERAGE(C12:C15)</f>
         <v>5.875</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G11" s="10">
+        <f>D11</f>
+        <v>0.05</v>
+      </c>
+      <c r="H11" s="9">
+        <f>E11</f>
+        <v>5.875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>34</v>
       </c>
@@ -603,7 +634,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>36</v>
       </c>
@@ -611,14 +642,14 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -635,11 +666,19 @@
         <f>C17</f>
         <v>5.875</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G17" s="10">
+        <f>D17+G11</f>
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="9">
+        <f>(D17*E17+G11*H11)/G17</f>
+        <v>5.875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B18" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -651,8 +690,16 @@
         <f>AVERAGE(C22:C25)</f>
         <v>5.583333333333333</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G21" s="10">
+        <f>D21+G17</f>
+        <v>0.25</v>
+      </c>
+      <c r="H21" s="9">
+        <f>(D21*E21+G17*H17)/G21</f>
+        <v>5.6999999999999993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B22" s="1" t="s">
         <v>5</v>
       </c>
@@ -660,7 +707,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
@@ -668,7 +715,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>33</v>
       </c>
@@ -676,10 +723,10 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B25" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -691,8 +738,16 @@
         <f>AVERAGE(C28:C31)</f>
         <v>5.5</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G27" s="10">
+        <f>D27+G21</f>
+        <v>0.4</v>
+      </c>
+      <c r="H27" s="9">
+        <f>(D27*E27+G21*H21)/G27</f>
+        <v>5.625</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B28" s="1" t="s">
         <v>16</v>
       </c>
@@ -700,7 +755,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B29" s="1" t="s">
         <v>17</v>
       </c>
@@ -711,7 +766,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>33</v>
       </c>
@@ -719,13 +774,13 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B32" s="1"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -735,76 +790,93 @@
       <c r="D33" s="5">
         <v>0.1</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="9">
         <f>AVERAGE(C34:C42)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+        <v>5.46875</v>
+      </c>
+      <c r="G33" s="10">
+        <f>D33+G27</f>
+        <v>0.5</v>
+      </c>
+      <c r="H33" s="9">
+        <f>(D33*E33+G27*H27)/G33</f>
+        <v>5.59375</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>19</v>
       </c>
       <c r="C34" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C35" s="8">
+        <v>5.75</v>
+      </c>
+      <c r="F35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>29</v>
       </c>
       <c r="C37" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C38" s="8">
+        <v>5.25</v>
+      </c>
+      <c r="F38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C39" s="8">
+        <v>5.25</v>
+      </c>
+      <c r="F39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>32</v>
       </c>
       <c r="C41" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -817,12 +889,22 @@
       <c r="D44" s="5">
         <v>0.1</v>
       </c>
-      <c r="E44" s="2">
-        <f>C44</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E44" s="8">
+        <v>5.35</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="10">
+        <f>D44+G33</f>
+        <v>0.6</v>
+      </c>
+      <c r="H44" s="9">
+        <f>(D44*E44+G33*H33)/G44</f>
+        <v>5.5531250000000005</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -831,23 +913,23 @@
       </c>
       <c r="E46" s="2">
         <f>AVERAGE(C47:C52)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
@@ -855,7 +937,7 @@
         <v>27</v>
       </c>
       <c r="C49" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
@@ -863,7 +945,7 @@
         <v>25</v>
       </c>
       <c r="C50" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
@@ -871,7 +953,7 @@
         <v>26</v>
       </c>
       <c r="C51" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
@@ -879,7 +961,7 @@
         <v>11</v>
       </c>
       <c r="C52" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
@@ -890,14 +972,14 @@
         <v>9</v>
       </c>
       <c r="C55" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D55" s="5">
         <v>0.1</v>
       </c>
       <c r="E55" s="2">
         <f>C55</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.45">
@@ -911,7 +993,7 @@
       </c>
       <c r="E58" s="4">
         <f>D11*E11+D17*E17+D21*E21+D27*E27+D33*E33+D44*E44+D46*E46+D55*E55</f>
-        <v>4.6500000000000004</v>
+        <v>3.3318750000000001</v>
       </c>
     </row>
   </sheetData>
